--- a/DSA/Assignment 3/sheets/Question3.xlsx
+++ b/DSA/Assignment 3/sheets/Question3.xlsx
@@ -59,19 +59,16 @@
     </font>
     <font>
       <sz val="13"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -118,17 +115,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -216,23 +209,15 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="DejaVu Sans"/>
               </a:rPr>
               <a:t>Pair Sum Problem Execution Time
-Q3: Pair Sum Problem (O(N 2 ))</a:t>
+Q3: Pair Sum Problem (O(N 2))</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -247,8 +232,8 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -280,16 +265,11 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
-                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -303,10 +283,11 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
-          <c:cat>
-            <c:strRef>
+          <c:xVal>
+            <c:numRef>
               <c:f>Question3!$A$2:$A$8</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
@@ -329,10 +310,10 @@
                 <c:pt idx="6">
                   <c:v>500</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>Question3!$B$2:$B$8</c:f>
               <c:numCache>
@@ -361,22 +342,14 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:hiLowLines>
-          <c:spPr>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:hiLowLines>
-        <c:marker val="1"/>
-        <c:axId val="1887845"/>
-        <c:axId val="22404665"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1887845"/>
+        <c:axId val="92298364"/>
+        <c:axId val="22077749"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="92298364"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -390,20 +363,12 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
-                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
-                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>N (Array Size)</a:t>
                 </a:r>
@@ -418,7 +383,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -435,24 +400,17 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22404665"/>
+        <c:crossAx val="22077749"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
+        <c:crossBetween val="between"/>
+      </c:valAx>
       <c:valAx>
-        <c:axId val="22404665"/>
+        <c:axId val="22077749"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -475,20 +433,12 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
-                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
-                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Execution Time (ns)</a:t>
                 </a:r>
@@ -503,7 +453,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -520,18 +470,14 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1887845"/>
+        <c:crossAx val="92298364"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -543,7 +489,7 @@
       </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
+    <c:dispBlanksAs val="span"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -560,16 +506,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>151200</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>86760</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>336240</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>56880</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>153000</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>162360</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -577,8 +523,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="1451520"/>
-        <a:ext cx="5759280" cy="3644640"/>
+        <a:off x="2258640" y="172080"/>
+        <a:ext cx="5755680" cy="3241440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -710,66 +656,66 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>969</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="1" t="n">
         <v>3492</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>12080</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1" t="n">
         <v>15041</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="1" t="n">
         <v>28148</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="1" t="n">
         <v>85265</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="1" t="n">
         <v>213348</v>
       </c>
     </row>
